--- a/模板/记录册模板.xlsx
+++ b/模板/记录册模板.xlsx
@@ -7,10 +7,10 @@
     <workbookView windowWidth="28800" windowHeight="11805"/>
   </bookViews>
   <sheets>
-    <sheet name="sheet1" sheetId="81" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">sheet1!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="60">
+  <si>
+    <t>委外单位：广州航驿停车场管理有限公司
+岗位/部门：xx员/xx部
+姓名:xxx</t>
+  </si>
   <si>
     <t>员 工 培 训 记 录</t>
   </si>
@@ -63,7 +68,7 @@
     <t>本次培训结果</t>
   </si>
   <si>
-    <t>确认人（即本次培训组织人）签名</t>
+    <t>确认人（即本次培训组织人）</t>
   </si>
   <si>
     <t>通识</t>
@@ -102,121 +107,112 @@
     <t>未通过需重训</t>
   </si>
   <si>
+    <t>股份员工准入培训</t>
+  </si>
+  <si>
+    <t>安全教育（股份）</t>
+  </si>
+  <si>
+    <t>√</t>
+  </si>
+  <si>
+    <t>运行管理部</t>
+  </si>
+  <si>
+    <t>线上培训</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>白云机场新入职员工服务培训（股份）</t>
+  </si>
+  <si>
+    <t>火灾的预防与应对——消防培训（股份）</t>
+  </si>
+  <si>
+    <t>《首问责任》（股份）</t>
+  </si>
+  <si>
+    <t>春风服务与志愿服务（股份）</t>
+  </si>
+  <si>
+    <t>委外员工准入资格培训（股份）</t>
+  </si>
+  <si>
+    <t>公共区员工资质培训</t>
+  </si>
+  <si>
+    <t>安全通识（公共区）</t>
+  </si>
+  <si>
+    <t>陈集龙</t>
+  </si>
+  <si>
+    <t>服务通识（公共区）</t>
+  </si>
+  <si>
+    <t>鹿婷婷</t>
+  </si>
+  <si>
+    <t>基本通识（公共区）</t>
+  </si>
+  <si>
+    <t>邓婕</t>
+  </si>
+  <si>
     <t>岗位安全通识培训</t>
   </si>
   <si>
+    <t>运行管理部第一堂安全课</t>
+  </si>
+  <si>
     <t>消防安全</t>
   </si>
   <si>
-    <t>√</t>
-  </si>
-  <si>
-    <t>运行管理部</t>
+    <t>反诈骗教育培训</t>
+  </si>
+  <si>
+    <t>治安管理处罚法</t>
+  </si>
+  <si>
+    <t>岗位技能培训</t>
+  </si>
+  <si>
+    <t>岗位手册培训</t>
+  </si>
+  <si>
+    <t>宿舍安全</t>
+  </si>
+  <si>
+    <t>反恐安全</t>
+  </si>
+  <si>
+    <t>交通安全</t>
+  </si>
+  <si>
+    <t>电梯安全</t>
+  </si>
+  <si>
+    <t>急救培训</t>
+  </si>
+  <si>
+    <t>典型不安全事件警示教育</t>
   </si>
   <si>
     <t>P8停车楼</t>
   </si>
   <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>交通安全</t>
-  </si>
-  <si>
-    <t>宿舍安全</t>
-  </si>
-  <si>
-    <t>反恐安全</t>
-  </si>
-  <si>
-    <t>电梯安全</t>
-  </si>
-  <si>
-    <t>自然灾害</t>
-  </si>
-  <si>
-    <t>公共区员工资质培训</t>
-  </si>
-  <si>
-    <t>安全通识（公共区）</t>
-  </si>
-  <si>
-    <t>陈集龙</t>
-  </si>
-  <si>
-    <t>服务通识（公共区）</t>
-  </si>
-  <si>
-    <t>鹿婷婷</t>
-  </si>
-  <si>
-    <t>基本通识（公共区）</t>
-  </si>
-  <si>
-    <t>黄伟</t>
-  </si>
-  <si>
-    <t>股份员工准入培训</t>
-  </si>
-  <si>
-    <t>安全教育（股份）</t>
-  </si>
-  <si>
-    <t>安全监察部</t>
-  </si>
-  <si>
-    <t>白云机场新入职员工服务培训（股份）</t>
-  </si>
-  <si>
-    <t>服务品质部</t>
-  </si>
-  <si>
-    <t>火灾的预防与应对——消防培训（股份）</t>
-  </si>
-  <si>
-    <t>潘俊杰</t>
-  </si>
-  <si>
-    <t>《首问责任》（股份）</t>
-  </si>
-  <si>
-    <t>客户服务中心</t>
-  </si>
-  <si>
-    <t>春风服务与志愿服务（股份）</t>
-  </si>
-  <si>
-    <t>委外员工准入资格培训（股份）</t>
-  </si>
-  <si>
-    <t>人力资源部</t>
-  </si>
-  <si>
-    <t>安全法律法规培训</t>
-  </si>
-  <si>
-    <t>治安管理处罚法</t>
-  </si>
-  <si>
-    <t>安全生产法解读</t>
-  </si>
-  <si>
-    <t>职业健康教育</t>
-  </si>
-  <si>
-    <t>职业健康</t>
-  </si>
-  <si>
-    <t>急救培训</t>
-  </si>
-  <si>
-    <t>安全技能培训</t>
+    <t>岗位实操培训</t>
   </si>
   <si>
     <t>灭火器、消火栓使用操作</t>
   </si>
   <si>
     <t>突发事件应急处置流程模拟实操</t>
+  </si>
+  <si>
+    <t>防暴器材实操/XX岗位技能培训</t>
   </si>
 </sst>
 </file>
@@ -230,7 +226,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,8 +251,40 @@
     </font>
     <font>
       <sz val="10"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="仿宋_GB2312"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -404,7 +432,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -413,6 +441,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -598,7 +632,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -627,21 +661,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="0"/>
-      </left>
-      <right style="thin">
-        <color indexed="0"/>
-      </right>
-      <top style="thin">
-        <color indexed="0"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -763,137 +782,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -915,17 +934,41 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1196,9 +1239,7 @@
   </tableStyles>
   <colors>
     <mruColors>
-      <color rgb="00FFFF00"/>
       <color rgb="00FF0000"/>
-      <color rgb="00FFFFFF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1458,36 +1499,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet26"/>
-  <dimension ref="A1:R25"/>
+  <sheetPr codeName="Sheet1">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.625" customWidth="1"/>
-    <col min="2" max="2" width="21.65" customWidth="1"/>
+    <col min="1" max="1" width="4.125" customWidth="1"/>
+    <col min="2" max="2" width="17.625" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
     <col min="4" max="5" width="4.25833333333333" customWidth="1"/>
     <col min="6" max="6" width="4" customWidth="1"/>
     <col min="7" max="7" width="15.0916666666667" customWidth="1"/>
-    <col min="8" max="8" width="15.625" customWidth="1"/>
+    <col min="8" max="8" width="15.1833333333333" customWidth="1"/>
     <col min="9" max="9" width="11.725" customWidth="1"/>
     <col min="10" max="10" width="5.75833333333333" customWidth="1"/>
     <col min="11" max="13" width="6.875" customWidth="1"/>
     <col min="14" max="14" width="11.875" customWidth="1"/>
     <col min="15" max="15" width="7.125" customWidth="1"/>
     <col min="16" max="16" width="6.25833333333333" customWidth="1"/>
-    <col min="17" max="17" width="6.50833333333333" customWidth="1"/>
+    <col min="17" max="17" width="6.5" customWidth="1"/>
     <col min="18" max="18" width="12.275" customWidth="1"/>
+    <col min="20" max="20" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1" spans="1:18">
-      <c r="A1" s="1"/>
+    <row r="1" ht="67" customHeight="1" spans="1:18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -1501,44 +1547,44 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
     </row>
-    <row r="2" ht="42" customHeight="1" spans="1:18">
+    <row r="2" ht="50" customHeight="1" spans="1:18">
       <c r="A2" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q2" s="4"/>
       <c r="R2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" ht="60" spans="1:18">
@@ -1546,997 +1592,1060 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3" s="5"/>
       <c r="P3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R3" s="5"/>
     </row>
-    <row r="4" ht="37" customHeight="1" spans="1:18">
+    <row r="4" ht="28" customHeight="1" spans="1:18">
       <c r="A4" s="4">
-        <f t="shared" ref="A4:A24" si="0">ROW()-3</f>
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="D4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="7">
-        <v>3.5</v>
+        <v>28</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O4" s="8"/>
-      <c r="P4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="O4" s="7"/>
+      <c r="P4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
     </row>
-    <row r="5" ht="37" customHeight="1" spans="1:18">
+    <row r="5" ht="28" customHeight="1" spans="1:18">
       <c r="A5" s="4">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="7">
-        <v>1.5</v>
+        <v>28</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="8"/>
+        <v>29</v>
+      </c>
+      <c r="O5" s="7"/>
       <c r="P5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
     </row>
-    <row r="6" ht="37" customHeight="1" spans="1:18">
+    <row r="6" ht="28" customHeight="1" spans="1:18">
       <c r="A6" s="4">
-        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:18">
+      <c r="A7" s="4">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="J6" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-    </row>
-    <row r="7" ht="37" customHeight="1" spans="1:18">
-      <c r="A7" s="4">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="7"/>
+      <c r="P7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:18">
+      <c r="A8" s="4">
+        <v>5</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="J7" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O7" s="8"/>
-      <c r="P7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-    </row>
-    <row r="8" ht="37" customHeight="1" spans="1:18">
-      <c r="A8" s="4">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="5">
+        <v>1</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:18">
+      <c r="A9" s="4">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="J8" s="7">
-        <v>1</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O8" s="8"/>
-      <c r="P8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-    </row>
-    <row r="9" ht="37" customHeight="1" spans="1:18">
-      <c r="A9" s="4">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="7">
+        <v>28</v>
+      </c>
+      <c r="J9" s="5">
         <v>1</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O9" s="8"/>
-      <c r="P9" s="4" t="s">
-        <v>25</v>
+      <c r="K9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9" s="4"/>
+      <c r="P9" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="Q9" s="5"/>
-      <c r="R9" s="4"/>
+      <c r="R9" s="5"/>
     </row>
-    <row r="10" ht="37" customHeight="1" spans="1:18">
+    <row r="10" ht="28" customHeight="1" spans="1:18">
       <c r="A10" s="4">
-        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J10" s="5">
         <v>1</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q10" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="Q10" s="5"/>
       <c r="R10" s="4"/>
     </row>
-    <row r="11" ht="37" customHeight="1" spans="1:18">
+    <row r="11" ht="28" customHeight="1" spans="1:18">
       <c r="A11" s="4">
-        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J11" s="5">
         <v>1</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q11" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="Q11" s="5"/>
       <c r="R11" s="4"/>
     </row>
-    <row r="12" ht="37" customHeight="1" spans="1:18">
+    <row r="12" ht="28" customHeight="1" spans="1:18">
       <c r="A12" s="4">
-        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J12" s="5">
         <v>1</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" ht="37" customHeight="1" spans="1:18">
+    <row r="13" ht="28" customHeight="1" spans="1:18">
       <c r="A13" s="4">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="5"/>
+      <c r="C13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="4"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J13" s="5">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="J13" s="10">
+        <v>3.5</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O13" s="8"/>
-      <c r="P13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
+        <v>29</v>
+      </c>
+      <c r="O13" s="11"/>
+      <c r="P13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
     </row>
-    <row r="14" ht="37" customHeight="1" spans="1:18">
+    <row r="14" ht="28" customHeight="1" spans="1:18">
       <c r="A14" s="4">
-        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="B14" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="5"/>
+      <c r="D14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="4"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J14" s="5">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="J14" s="10">
+        <v>1.5</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O14" s="8"/>
+        <v>29</v>
+      </c>
+      <c r="O14" s="11"/>
       <c r="P14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
     </row>
-    <row r="15" ht="37" customHeight="1" spans="1:18">
+    <row r="15" ht="28" customHeight="1" spans="1:18">
       <c r="A15" s="4">
-        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="5"/>
+      <c r="B15" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="4"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O15" s="11"/>
+      <c r="P15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:18">
+      <c r="A16" s="4">
+        <v>13</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="J15" s="5">
-        <v>1</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-    </row>
-    <row r="16" ht="37" customHeight="1" spans="1:18">
-      <c r="A16" s="4">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O16" s="11"/>
+      <c r="P16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:18">
+      <c r="A17" s="4">
+        <v>14</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O16" s="8"/>
-      <c r="P16" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-    </row>
-    <row r="17" ht="37" customHeight="1" spans="1:18">
-      <c r="A17" s="4">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="10">
+        <v>1</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O17" s="11"/>
+      <c r="P17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:18">
+      <c r="A18" s="4">
+        <v>15</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="J17" s="5">
-        <v>1</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-    </row>
-    <row r="18" ht="37" customHeight="1" spans="1:18">
-      <c r="A18" s="4">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="10">
+        <v>1</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O18" s="11"/>
+      <c r="P18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:18">
+      <c r="A19" s="4">
+        <v>16</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="J18" s="5">
-        <v>1</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O18" s="8"/>
-      <c r="P18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-    </row>
-    <row r="19" ht="37" customHeight="1" spans="1:18">
-      <c r="A19" s="4">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="10">
+        <v>2</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O19" s="11"/>
+      <c r="P19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:18">
+      <c r="A20" s="4">
+        <v>17</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="J19" s="7">
-        <v>2</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O19" s="8"/>
-      <c r="P19" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-    </row>
-    <row r="20" ht="37" customHeight="1" spans="1:18">
-      <c r="A20" s="4">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="10">
+        <v>2</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20" s="11"/>
+      <c r="P20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:18">
+      <c r="A21" s="4">
+        <v>18</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="J20" s="7">
-        <v>2</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O20" s="8"/>
-      <c r="P20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-    </row>
-    <row r="21" ht="37" customHeight="1" spans="1:18">
-      <c r="A21" s="4">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21" s="10">
+        <v>1</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21" s="11"/>
+      <c r="P21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:18">
+      <c r="A22" s="4">
+        <v>19</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="J21" s="7">
-        <v>1</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O21" s="8"/>
-      <c r="P21" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-    </row>
-    <row r="22" ht="37" customHeight="1" spans="1:18">
-      <c r="A22" s="4">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" s="10">
+        <v>1</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O22" s="11"/>
+      <c r="P22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:18">
+      <c r="A23" s="4">
+        <v>20</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="J22" s="7">
-        <v>1</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O22" s="8"/>
-      <c r="P22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-    </row>
-    <row r="23" ht="37" customHeight="1" spans="1:18">
-      <c r="A23" s="4">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" s="10">
+        <v>4</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O23" s="11"/>
+      <c r="P23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:18">
+      <c r="A24" s="4">
+        <v>21</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="J23" s="7">
-        <v>4</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N23" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O23" s="8"/>
-      <c r="P23" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-    </row>
-    <row r="24" ht="37" customHeight="1" spans="1:18">
-      <c r="A24" s="4">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J24" s="10">
+        <v>4</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O24" s="11"/>
+      <c r="P24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:18">
+      <c r="A25" s="4">
+        <v>22</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="7">
+      <c r="H25" s="6"/>
+      <c r="I25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J25" s="5">
         <v>4</v>
       </c>
-      <c r="K24" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N24" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O24" s="8"/>
-      <c r="P24" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
+      <c r="K25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O25" s="11"/>
+      <c r="P25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="4"/>
     </row>
-    <row r="25" ht="24" customHeight="1"/>
+    <row r="26" ht="28" customHeight="1" spans="1:18">
+      <c r="A26" s="4">
+        <v>23</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J26" s="4">
+        <v>6</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O26" s="11"/>
+      <c r="P26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+    </row>
   </sheetData>
-  <sortState ref="A5:P35">
-    <sortCondition ref="H5:H35"/>
-  </sortState>
   <mergeCells count="12">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:R1"/>
@@ -2551,8 +2660,8 @@
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="R2:R3"/>
   </mergeCells>
-  <pageMargins left="0.472222222222222" right="0.25" top="0.156944444444444" bottom="0.156944444444444" header="0.297916666666667" footer="0.297916666666667"/>
-  <pageSetup paperSize="9" scale="60" fitToHeight="0" orientation="landscape" horizontalDpi="600"/>
+  <pageMargins left="0.751388888888889" right="0.751388888888889" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="76" fitToHeight="0" orientation="landscape" horizontalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/模板/记录册模板.xlsx
+++ b/模板/记录册模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11805"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,7 +131,7 @@
     <t>火灾的预防与应对——消防培训（股份）</t>
   </si>
   <si>
-    <t>《首问责任》（股份）</t>
+    <t>《首问责任》（股份）/春风服务与志愿服务（股份）</t>
   </si>
   <si>
     <t>春风服务与志愿服务（股份）</t>
@@ -226,10 +226,17 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -252,6 +259,13 @@
     <font>
       <sz val="10"/>
       <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -273,13 +287,6 @@
       <color theme="4"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -782,192 +789,204 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1524,1126 +1543,1126 @@
   </cols>
   <sheetData>
     <row r="1" ht="67" customHeight="1" spans="1:18">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
     </row>
     <row r="2" ht="50" customHeight="1" spans="1:18">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5" t="s">
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5" t="s">
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="5" t="s">
+      <c r="Q2" s="5"/>
+      <c r="R2" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" ht="60" spans="1:18">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5" t="s">
+      <c r="J3" s="6"/>
+      <c r="K3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="5"/>
-      <c r="P3" s="4" t="s">
+      <c r="O3" s="6"/>
+      <c r="P3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="R3" s="5"/>
+      <c r="R3" s="6"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:18">
-      <c r="A4" s="4">
+      <c r="A4" s="5">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5" t="s">
+      <c r="D4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="4" t="s">
+      <c r="H4" s="7"/>
+      <c r="I4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="6">
         <v>1</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" s="7"/>
-      <c r="P4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
+      <c r="K4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="8"/>
+      <c r="P4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:18">
-      <c r="A5" s="4">
+      <c r="A5" s="5">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5" t="s">
+      <c r="D5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="4" t="s">
+      <c r="H5" s="7"/>
+      <c r="I5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="6">
         <v>1</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" s="7"/>
-      <c r="P5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
+      <c r="K5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="8"/>
+      <c r="P5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:18">
-      <c r="A6" s="4">
+      <c r="A6" s="5">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5" t="s">
+      <c r="D6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="4" t="s">
+      <c r="H6" s="7"/>
+      <c r="I6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="6">
         <v>1</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O6" s="7"/>
-      <c r="P6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
+      <c r="K6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" s="8"/>
+      <c r="P6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:18">
-      <c r="A7" s="4">
+      <c r="A7" s="5">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5" t="s">
+      <c r="D7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="4" t="s">
+      <c r="H7" s="7"/>
+      <c r="I7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" s="7"/>
-      <c r="P7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
+      <c r="J7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="8"/>
+      <c r="P7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="1:18">
-      <c r="A8" s="4">
+    <row r="8" s="1" customFormat="1" ht="28" customHeight="1" spans="1:18">
+      <c r="A8" s="9">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5" t="s">
+      <c r="D8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="4" t="s">
+      <c r="H8" s="11"/>
+      <c r="I8" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="10">
         <v>1</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
+      <c r="K8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:18">
-      <c r="A9" s="4">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="A9" s="5">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
+      <c r="D9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="4" t="s">
+      <c r="H9" s="7"/>
+      <c r="I9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="6">
         <v>1</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O9" s="4"/>
-      <c r="P9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
+      <c r="K9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9" s="5"/>
+      <c r="P9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:18">
-      <c r="A10" s="4">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="A10" s="5">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5" t="s">
+      <c r="D10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="4" t="s">
+      <c r="H10" s="7"/>
+      <c r="I10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="6">
         <v>1</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O10" s="8"/>
-      <c r="P10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="4"/>
+      <c r="K10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" s="13"/>
+      <c r="P10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="5"/>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:18">
-      <c r="A11" s="4">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="5">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5" t="s">
+      <c r="D11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="4" t="s">
+      <c r="H11" s="7"/>
+      <c r="I11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="6">
         <v>1</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O11" s="8"/>
-      <c r="P11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="4"/>
+      <c r="K11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" s="13"/>
+      <c r="P11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="5"/>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:18">
-      <c r="A12" s="4">
-        <v>9</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="5">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5" t="s">
+      <c r="D12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="4" t="s">
+      <c r="H12" s="7"/>
+      <c r="I12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="6">
         <v>1</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
+      <c r="K12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12" s="13"/>
+      <c r="P12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:18">
-      <c r="A13" s="4">
-        <v>10</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="A13" s="5">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5" t="s">
+      <c r="D13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="4" t="s">
+      <c r="H13" s="7"/>
+      <c r="I13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="15">
         <v>3.5</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
+      <c r="K13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O13" s="16"/>
+      <c r="P13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:18">
-      <c r="A14" s="4">
-        <v>11</v>
-      </c>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="5">
+        <v>10</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5" t="s">
+      <c r="D14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="4" t="s">
+      <c r="H14" s="7"/>
+      <c r="I14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="15">
         <v>1.5</v>
       </c>
-      <c r="K14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" s="11"/>
-      <c r="P14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
+      <c r="K14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" s="16"/>
+      <c r="P14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:18">
-      <c r="A15" s="4">
-        <v>12</v>
-      </c>
-      <c r="B15" s="12" t="s">
+      <c r="A15" s="5">
+        <v>11</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5" t="s">
+      <c r="D15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="4" t="s">
+      <c r="H15" s="7"/>
+      <c r="I15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="15">
         <v>1.5</v>
       </c>
-      <c r="K15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
+      <c r="K15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O15" s="16"/>
+      <c r="P15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:18">
-      <c r="A16" s="4">
-        <v>13</v>
-      </c>
-      <c r="B16" s="12" t="s">
+      <c r="A16" s="5">
+        <v>12</v>
+      </c>
+      <c r="B16" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="5" t="s">
+      <c r="D16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="4" t="s">
+      <c r="H16" s="7"/>
+      <c r="I16" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="15">
         <v>1.5</v>
       </c>
-      <c r="K16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O16" s="11"/>
-      <c r="P16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
+      <c r="K16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O16" s="16"/>
+      <c r="P16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:18">
-      <c r="A17" s="4">
-        <v>14</v>
-      </c>
-      <c r="B17" s="13" t="s">
+      <c r="A17" s="5">
+        <v>13</v>
+      </c>
+      <c r="B17" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="5" t="s">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H17" s="6"/>
-      <c r="I17" s="4" t="s">
+      <c r="H17" s="7"/>
+      <c r="I17" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="15">
         <v>1</v>
       </c>
-      <c r="K17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O17" s="11"/>
-      <c r="P17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
+      <c r="K17" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O17" s="16"/>
+      <c r="P17" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:18">
-      <c r="A18" s="4">
-        <v>15</v>
-      </c>
-      <c r="B18" s="13" t="s">
+      <c r="A18" s="5">
+        <v>14</v>
+      </c>
+      <c r="B18" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="5" t="s">
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="4" t="s">
+      <c r="H18" s="7"/>
+      <c r="I18" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="15">
         <v>1</v>
       </c>
-      <c r="K18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O18" s="11"/>
-      <c r="P18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
+      <c r="K18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O18" s="16"/>
+      <c r="P18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:18">
-      <c r="A19" s="4">
-        <v>16</v>
-      </c>
-      <c r="B19" s="13" t="s">
+      <c r="A19" s="5">
+        <v>15</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="5" t="s">
+      <c r="D19" s="5"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="6"/>
-      <c r="I19" s="4" t="s">
+      <c r="H19" s="7"/>
+      <c r="I19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="15">
         <v>2</v>
       </c>
-      <c r="K19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O19" s="11"/>
-      <c r="P19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
+      <c r="K19" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O19" s="16"/>
+      <c r="P19" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:18">
-      <c r="A20" s="4">
-        <v>17</v>
-      </c>
-      <c r="B20" s="13" t="s">
+      <c r="A20" s="5">
+        <v>16</v>
+      </c>
+      <c r="B20" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="5" t="s">
+      <c r="D20" s="5"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="4" t="s">
+      <c r="H20" s="7"/>
+      <c r="I20" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="15">
         <v>2</v>
       </c>
-      <c r="K20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O20" s="11"/>
-      <c r="P20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
+      <c r="K20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20" s="16"/>
+      <c r="P20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:18">
-      <c r="A21" s="4">
-        <v>18</v>
-      </c>
-      <c r="B21" s="13" t="s">
+      <c r="A21" s="5">
+        <v>17</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="5" t="s">
+      <c r="D21" s="5"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H21" s="6"/>
-      <c r="I21" s="4" t="s">
+      <c r="H21" s="7"/>
+      <c r="I21" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="15">
         <v>1</v>
       </c>
-      <c r="K21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O21" s="11"/>
-      <c r="P21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
+      <c r="K21" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21" s="16"/>
+      <c r="P21" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:18">
-      <c r="A22" s="4">
-        <v>19</v>
-      </c>
-      <c r="B22" s="13" t="s">
+      <c r="A22" s="5">
+        <v>18</v>
+      </c>
+      <c r="B22" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="D22" s="5"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H22" s="6"/>
-      <c r="I22" s="4" t="s">
+      <c r="H22" s="7"/>
+      <c r="I22" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="15">
         <v>1</v>
       </c>
-      <c r="K22" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O22" s="11"/>
-      <c r="P22" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
+      <c r="K22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O22" s="16"/>
+      <c r="P22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:18">
-      <c r="A23" s="4">
-        <v>20</v>
-      </c>
-      <c r="B23" s="13" t="s">
+      <c r="A23" s="5">
+        <v>19</v>
+      </c>
+      <c r="B23" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="5" t="s">
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H23" s="6"/>
-      <c r="I23" s="4" t="s">
+      <c r="H23" s="7"/>
+      <c r="I23" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="15">
         <v>4</v>
       </c>
-      <c r="K23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N23" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O23" s="11"/>
-      <c r="P23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
+      <c r="K23" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O23" s="16"/>
+      <c r="P23" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:18">
-      <c r="A24" s="4">
-        <v>21</v>
-      </c>
-      <c r="B24" s="16" t="s">
+      <c r="A24" s="5">
+        <v>20</v>
+      </c>
+      <c r="B24" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="5" t="s">
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H24" s="6"/>
-      <c r="I24" s="4" t="s">
+      <c r="H24" s="7"/>
+      <c r="I24" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="15">
         <v>4</v>
       </c>
-      <c r="K24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N24" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O24" s="11"/>
-      <c r="P24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
+      <c r="K24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O24" s="16"/>
+      <c r="P24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:18">
-      <c r="A25" s="4">
-        <v>22</v>
-      </c>
-      <c r="B25" s="18" t="s">
+      <c r="A25" s="5">
+        <v>21</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="5" t="s">
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H25" s="6"/>
-      <c r="I25" s="4" t="s">
+      <c r="H25" s="7"/>
+      <c r="I25" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="5">
+      <c r="J25" s="6">
         <v>4</v>
       </c>
-      <c r="K25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O25" s="11"/>
-      <c r="P25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="4"/>
+      <c r="K25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O25" s="16"/>
+      <c r="P25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="5"/>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:18">
-      <c r="A26" s="4">
-        <v>23</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="17" t="s">
+      <c r="A26" s="5">
+        <v>22</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="5" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H26" s="6"/>
-      <c r="I26" s="4" t="s">
+      <c r="H26" s="7"/>
+      <c r="I26" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="4">
+      <c r="J26" s="5">
         <v>6</v>
       </c>
-      <c r="K26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O26" s="11"/>
-      <c r="P26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
+      <c r="K26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O26" s="16"/>
+      <c r="P26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/模板/记录册模板.xlsx
+++ b/模板/记录册模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="14400" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="60">
   <si>
     <t>委外单位：广州航驿停车场管理有限公司
 岗位/部门：xx员/xx部
@@ -1804,8 +1804,8 @@
       <c r="I7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="6" t="s">
-        <v>29</v>
+      <c r="J7" s="6">
+        <v>1</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>29</v>
@@ -2071,7 +2071,7 @@
         <v>28</v>
       </c>
       <c r="J13" s="15">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>26</v>
@@ -2115,7 +2115,7 @@
         <v>28</v>
       </c>
       <c r="J14" s="15">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>26</v>
@@ -2159,7 +2159,7 @@
         <v>28</v>
       </c>
       <c r="J15" s="15">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>26</v>
@@ -2203,7 +2203,7 @@
         <v>28</v>
       </c>
       <c r="J16" s="15">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>26</v>
@@ -2247,7 +2247,7 @@
         <v>28</v>
       </c>
       <c r="J17" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>26</v>
@@ -2291,7 +2291,7 @@
         <v>28</v>
       </c>
       <c r="J18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>26</v>
@@ -2467,7 +2467,7 @@
         <v>28</v>
       </c>
       <c r="J22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>26</v>
@@ -2511,7 +2511,7 @@
         <v>55</v>
       </c>
       <c r="J23" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>26</v>
@@ -2555,7 +2555,7 @@
         <v>55</v>
       </c>
       <c r="J24" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>26</v>
@@ -2599,7 +2599,7 @@
         <v>55</v>
       </c>
       <c r="J25" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K25" s="5" t="s">
         <v>26</v>
@@ -2643,7 +2643,7 @@
         <v>55</v>
       </c>
       <c r="J26" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>26</v>

--- a/模板/记录册模板.xlsx
+++ b/模板/记录册模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="14400" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11805"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="64">
   <si>
     <t>委外单位：广州航驿停车场管理有限公司
 岗位/部门：xx员/xx部
@@ -116,30 +116,45 @@
     <t>√</t>
   </si>
   <si>
+    <t>安全监察部</t>
+  </si>
+  <si>
+    <t>P8停车楼</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>白云机场新入职员工服务培训（股份）</t>
+  </si>
+  <si>
+    <t>服务品质部</t>
+  </si>
+  <si>
+    <t>火灾的预防与应对——消防培训（股份）</t>
+  </si>
+  <si>
+    <t>潘俊杰</t>
+  </si>
+  <si>
+    <t>《首问责任》（股份）/春风服务与志愿服务（股份）</t>
+  </si>
+  <si>
+    <t>客户服务中心</t>
+  </si>
+  <si>
+    <t>春风服务与志愿服务（股份）</t>
+  </si>
+  <si>
+    <t>人力资源部</t>
+  </si>
+  <si>
+    <t>委外员工准入资格培训（股份）</t>
+  </si>
+  <si>
     <t>运行管理部</t>
   </si>
   <si>
-    <t>线上培训</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>白云机场新入职员工服务培训（股份）</t>
-  </si>
-  <si>
-    <t>火灾的预防与应对——消防培训（股份）</t>
-  </si>
-  <si>
-    <t>《首问责任》（股份）/春风服务与志愿服务（股份）</t>
-  </si>
-  <si>
-    <t>春风服务与志愿服务（股份）</t>
-  </si>
-  <si>
-    <t>委外员工准入资格培训（股份）</t>
-  </si>
-  <si>
     <t>公共区员工资质培训</t>
   </si>
   <si>
@@ -198,9 +213,6 @@
   </si>
   <si>
     <t>典型不安全事件警示教育</t>
-  </si>
-  <si>
-    <t>P8停车楼</t>
   </si>
   <si>
     <t>岗位实操培训</t>
@@ -1710,7 +1722,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="5" t="s">
@@ -1746,7 +1758,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>26</v>
@@ -1754,7 +1766,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="5" t="s">
@@ -1790,7 +1802,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>26</v>
@@ -1798,7 +1810,7 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="5" t="s">
@@ -1834,7 +1846,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>26</v>
@@ -1842,7 +1854,7 @@
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="9" t="s">
@@ -1880,7 +1892,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>26</v>
@@ -1888,7 +1900,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="5" t="s">
@@ -1921,10 +1933,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>26</v>
@@ -1932,7 +1944,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="5" t="s">
@@ -1965,10 +1977,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>26</v>
@@ -1976,7 +1988,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="5" t="s">
@@ -2009,10 +2021,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>26</v>
@@ -2020,7 +2032,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="5" t="s">
@@ -2053,10 +2065,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>26</v>
@@ -2064,7 +2076,7 @@
       <c r="E13" s="5"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="5" t="s">
@@ -2097,10 +2109,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>26</v>
@@ -2108,7 +2120,7 @@
       <c r="E14" s="5"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="5" t="s">
@@ -2141,10 +2153,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>26</v>
@@ -2152,7 +2164,7 @@
       <c r="E15" s="5"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="5" t="s">
@@ -2185,10 +2197,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>26</v>
@@ -2196,7 +2208,7 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="5" t="s">
@@ -2229,10 +2241,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -2240,7 +2252,7 @@
         <v>26</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="5" t="s">
@@ -2273,10 +2285,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -2284,7 +2296,7 @@
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="5" t="s">
@@ -2317,10 +2329,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="20"/>
@@ -2328,7 +2340,7 @@
         <v>26</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="5" t="s">
@@ -2361,10 +2373,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="20"/>
@@ -2372,7 +2384,7 @@
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="5" t="s">
@@ -2405,10 +2417,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="20"/>
@@ -2416,7 +2428,7 @@
         <v>26</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="5" t="s">
@@ -2449,10 +2461,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="20"/>
@@ -2460,7 +2472,7 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="5" t="s">
@@ -2493,10 +2505,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D23" s="20"/>
       <c r="E23" s="20"/>
@@ -2504,11 +2516,11 @@
         <v>26</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="5" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="J23" s="15">
         <v>2</v>
@@ -2537,10 +2549,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D24" s="20"/>
       <c r="E24" s="20"/>
@@ -2548,11 +2560,11 @@
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="5" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="J24" s="15">
         <v>1</v>
@@ -2581,10 +2593,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -2592,11 +2604,11 @@
         <v>26</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="5" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="J25" s="6">
         <v>1</v>
@@ -2625,10 +2637,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -2636,11 +2648,11 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="5" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="J26" s="5">
         <v>2</v>

--- a/模板/记录册模板.xlsx
+++ b/模板/记录册模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11805"/>
+    <workbookView windowWidth="14400" windowHeight="11805"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="64">
   <si>
     <t>委外单位：广州航驿停车场管理有限公司
 岗位/部门：xx员/xx部
@@ -146,40 +146,40 @@
     <t>春风服务与志愿服务（股份）</t>
   </si>
   <si>
+    <t>委外员工准入资格培训（股份）</t>
+  </si>
+  <si>
     <t>人力资源部</t>
   </si>
   <si>
-    <t>委外员工准入资格培训（股份）</t>
+    <t>公共区员工资质培训</t>
+  </si>
+  <si>
+    <t>安全通识（公共区）</t>
+  </si>
+  <si>
+    <t>陈集龙</t>
+  </si>
+  <si>
+    <t>服务通识（公共区）</t>
+  </si>
+  <si>
+    <t>鹿婷婷</t>
+  </si>
+  <si>
+    <t>基本通识（公共区）</t>
+  </si>
+  <si>
+    <t>邓婕</t>
+  </si>
+  <si>
+    <t>岗位安全通识培训</t>
+  </si>
+  <si>
+    <t>运行管理部第一堂安全课</t>
   </si>
   <si>
     <t>运行管理部</t>
-  </si>
-  <si>
-    <t>公共区员工资质培训</t>
-  </si>
-  <si>
-    <t>安全通识（公共区）</t>
-  </si>
-  <si>
-    <t>陈集龙</t>
-  </si>
-  <si>
-    <t>服务通识（公共区）</t>
-  </si>
-  <si>
-    <t>鹿婷婷</t>
-  </si>
-  <si>
-    <t>基本通识（公共区）</t>
-  </si>
-  <si>
-    <t>邓婕</t>
-  </si>
-  <si>
-    <t>岗位安全通识培训</t>
-  </si>
-  <si>
-    <t>运行管理部第一堂安全课</t>
   </si>
   <si>
     <t>消防安全</t>
@@ -1853,9 +1853,7 @@
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
-      <c r="G8" s="10" t="s">
-        <v>37</v>
-      </c>
+      <c r="G8" s="10"/>
       <c r="H8" s="11"/>
       <c r="I8" s="9" t="s">
         <v>28</v>
@@ -1892,7 +1890,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>26</v>
@@ -1900,7 +1898,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="5" t="s">
@@ -1933,10 +1931,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>26</v>
@@ -1944,7 +1942,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="5" t="s">
@@ -1977,10 +1975,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>26</v>
@@ -1988,7 +1986,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="5" t="s">
@@ -2021,10 +2019,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>26</v>
@@ -2032,7 +2030,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="5" t="s">
@@ -2065,10 +2063,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>47</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>48</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>26</v>
@@ -2076,7 +2074,7 @@
       <c r="E13" s="5"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="5" t="s">
@@ -2109,7 +2107,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>49</v>
@@ -2120,7 +2118,7 @@
       <c r="E14" s="5"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="5" t="s">
@@ -2153,7 +2151,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>50</v>
@@ -2164,7 +2162,7 @@
       <c r="E15" s="5"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="5" t="s">
@@ -2197,7 +2195,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>51</v>
@@ -2208,7 +2206,7 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="5" t="s">
@@ -2252,7 +2250,7 @@
         <v>26</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="5" t="s">
@@ -2296,7 +2294,7 @@
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="5" t="s">
@@ -2340,7 +2338,7 @@
         <v>26</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="5" t="s">
@@ -2384,7 +2382,7 @@
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="5" t="s">
@@ -2428,7 +2426,7 @@
         <v>26</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="5" t="s">
@@ -2472,7 +2470,7 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="5" t="s">
@@ -2516,7 +2514,7 @@
         <v>26</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="5" t="s">
@@ -2560,7 +2558,7 @@
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="5" t="s">
@@ -2604,7 +2602,7 @@
         <v>26</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="5" t="s">
@@ -2648,7 +2646,7 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="5" t="s">
